--- a/output/roomself_excel/9392.xlsx
+++ b/output/roomself_excel/9392.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>112030</v>
+        <v>153786</v>
       </c>
       <c r="D2" t="n">
-        <v>2764</v>
+        <v>3172</v>
       </c>
       <c r="E2" t="n">
-        <v>959</v>
+        <v>339</v>
       </c>
       <c r="F2" t="n">
-        <v>382</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>15904</v>
+        <v>315958</v>
       </c>
       <c r="D3" t="n">
-        <v>1016</v>
+        <v>5396</v>
       </c>
       <c r="E3" t="n">
-        <v>112</v>
+        <v>710</v>
       </c>
       <c r="F3" t="n">
-        <v>16</v>
+        <v>479</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>597737</v>
+        <v>112030</v>
       </c>
       <c r="D4" t="n">
-        <v>10148</v>
+        <v>2764</v>
       </c>
       <c r="E4" t="n">
-        <v>1245</v>
+        <v>382</v>
       </c>
       <c r="F4" t="n">
-        <v>959</v>
+        <v>341</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>69907</v>
+        <v>280561</v>
       </c>
       <c r="D5" t="n">
-        <v>2308</v>
+        <v>5328</v>
       </c>
       <c r="E5" t="n">
-        <v>364</v>
+        <v>679</v>
       </c>
       <c r="F5" t="n">
-        <v>166</v>
+        <v>618</v>
       </c>
     </row>
     <row r="6">
@@ -558,16 +558,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>325457</v>
+        <v>91266</v>
       </c>
       <c r="D6" t="n">
-        <v>7124</v>
+        <v>2580</v>
       </c>
       <c r="E6" t="n">
-        <v>960</v>
+        <v>319</v>
       </c>
       <c r="F6" t="n">
-        <v>618</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>39825</v>
+        <v>94170</v>
       </c>
       <c r="D7" t="n">
-        <v>1608</v>
+        <v>2612</v>
       </c>
       <c r="E7" t="n">
-        <v>177</v>
+        <v>342</v>
       </c>
       <c r="F7" t="n">
-        <v>16</v>
+        <v>283</v>
       </c>
     </row>
     <row r="8">
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>153488</v>
+        <v>39825</v>
       </c>
       <c r="D8" t="n">
-        <v>3144</v>
+        <v>1608</v>
       </c>
       <c r="E8" t="n">
-        <v>455</v>
+        <v>177</v>
       </c>
       <c r="F8" t="n">
-        <v>362</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -620,17 +620,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>130384</v>
+        <v>36337</v>
       </c>
       <c r="D9" t="n">
-        <v>3196</v>
+        <v>1528</v>
       </c>
       <c r="E9" t="n">
-        <v>319</v>
+        <v>203</v>
       </c>
       <c r="F9" t="n">
         <v>16</v>
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6873</v>
+        <v>127993</v>
       </c>
       <c r="D10" t="n">
-        <v>664</v>
+        <v>3784</v>
       </c>
       <c r="E10" t="n">
-        <v>79</v>
+        <v>959</v>
       </c>
       <c r="F10" t="n">
-        <v>16</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>31059</v>
+        <v>51512</v>
       </c>
       <c r="D11" t="n">
-        <v>1424</v>
+        <v>2052</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>408</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
     </row>
     <row r="12">
@@ -686,20 +686,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>36337</v>
+        <v>172040</v>
       </c>
       <c r="D12" t="n">
-        <v>1528</v>
+        <v>3384</v>
       </c>
       <c r="E12" t="n">
-        <v>203</v>
+        <v>522</v>
       </c>
       <c r="F12" t="n">
-        <v>16</v>
+        <v>508</v>
       </c>
     </row>
     <row r="13">
@@ -708,17 +708,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>91266</v>
+        <v>15904</v>
       </c>
       <c r="D13" t="n">
-        <v>2580</v>
+        <v>1016</v>
       </c>
       <c r="E13" t="n">
-        <v>319</v>
+        <v>112</v>
       </c>
       <c r="F13" t="n">
         <v>16</v>
@@ -734,16 +734,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>283734</v>
+        <v>69907</v>
       </c>
       <c r="D14" t="n">
-        <v>4652</v>
+        <v>2308</v>
       </c>
       <c r="E14" t="n">
-        <v>960</v>
+        <v>364</v>
       </c>
       <c r="F14" t="n">
-        <v>589</v>
+        <v>166</v>
       </c>
     </row>
     <row r="15">
@@ -752,20 +752,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>94170</v>
+        <v>153488</v>
       </c>
       <c r="D15" t="n">
-        <v>2612</v>
+        <v>3144</v>
       </c>
       <c r="E15" t="n">
-        <v>342</v>
+        <v>455</v>
       </c>
       <c r="F15" t="n">
-        <v>283</v>
+        <v>362</v>
       </c>
     </row>
     <row r="16">
@@ -778,16 +778,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>123006</v>
+        <v>130384</v>
       </c>
       <c r="D16" t="n">
-        <v>2972</v>
+        <v>3196</v>
       </c>
       <c r="E16" t="n">
-        <v>510</v>
+        <v>319</v>
       </c>
       <c r="F16" t="n">
-        <v>265</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17">
@@ -796,20 +796,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>51512</v>
+        <v>6873</v>
       </c>
       <c r="D17" t="n">
-        <v>2052</v>
+        <v>664</v>
       </c>
       <c r="E17" t="n">
-        <v>408</v>
+        <v>79</v>
       </c>
       <c r="F17" t="n">
-        <v>153</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -818,20 +818,86 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>172040</v>
+        <v>31059</v>
       </c>
       <c r="D18" t="n">
-        <v>3384</v>
+        <v>1424</v>
       </c>
       <c r="E18" t="n">
-        <v>522</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>508</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>44896</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2320</v>
+      </c>
+      <c r="E19" t="n">
+        <v>92</v>
+      </c>
+      <c r="F19" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>283734</v>
+      </c>
+      <c r="D20" t="n">
+        <v>4652</v>
+      </c>
+      <c r="E20" t="n">
+        <v>589</v>
+      </c>
+      <c r="F20" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>123006</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2972</v>
+      </c>
+      <c r="E21" t="n">
+        <v>510</v>
+      </c>
+      <c r="F21" t="n">
+        <v>265</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/9392.xlsx
+++ b/output/roomself_excel/9392.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,12 +495,20 @@
       <c r="D2" t="n">
         <v>3172</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>339</v>
       </c>
-      <c r="F2" t="n">
-        <v>16</v>
-      </c>
+      <c r="G2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,11 +525,27 @@
       <c r="D3" t="n">
         <v>5396</v>
       </c>
-      <c r="E3" t="n">
-        <v>710</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>479</v>
+        <v>463</v>
+      </c>
+      <c r="G3" t="n">
+        <v>16</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>678</v>
+      </c>
+      <c r="J3" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -519,11 +563,27 @@
       <c r="D4" t="n">
         <v>2764</v>
       </c>
-      <c r="E4" t="n">
-        <v>382</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>341</v>
+        <v>366</v>
+      </c>
+      <c r="G4" t="n">
+        <v>16</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>325</v>
+      </c>
+      <c r="J4" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="5">
@@ -541,11 +601,27 @@
       <c r="D5" t="n">
         <v>5328</v>
       </c>
-      <c r="E5" t="n">
-        <v>679</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>618</v>
+        <v>301</v>
+      </c>
+      <c r="G5" t="n">
+        <v>16</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>647</v>
+      </c>
+      <c r="J5" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="6">
@@ -563,12 +639,20 @@
       <c r="D6" t="n">
         <v>2580</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>319</v>
       </c>
-      <c r="F6" t="n">
-        <v>16</v>
-      </c>
+      <c r="G6" t="n">
+        <v>16</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,11 +669,27 @@
       <c r="D7" t="n">
         <v>2612</v>
       </c>
-      <c r="E7" t="n">
-        <v>342</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>283</v>
+        <v>253</v>
+      </c>
+      <c r="G7" t="n">
+        <v>16</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>326</v>
+      </c>
+      <c r="J7" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="8">
@@ -607,12 +707,20 @@
       <c r="D8" t="n">
         <v>1608</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>177</v>
       </c>
-      <c r="F8" t="n">
-        <v>16</v>
-      </c>
+      <c r="G8" t="n">
+        <v>16</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +737,20 @@
       <c r="D9" t="n">
         <v>1528</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>203</v>
       </c>
-      <c r="F9" t="n">
-        <v>16</v>
-      </c>
+      <c r="G9" t="n">
+        <v>16</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +767,20 @@
       <c r="D10" t="n">
         <v>3784</v>
       </c>
-      <c r="E10" t="n">
-        <v>959</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F10" t="n">
         <v>177</v>
       </c>
+      <c r="G10" t="n">
+        <v>16</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,11 +797,27 @@
       <c r="D11" t="n">
         <v>2052</v>
       </c>
-      <c r="E11" t="n">
-        <v>408</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F11" t="n">
-        <v>153</v>
+        <v>376</v>
+      </c>
+      <c r="G11" t="n">
+        <v>16</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>274</v>
+      </c>
+      <c r="J11" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="12">
@@ -695,11 +835,27 @@
       <c r="D12" t="n">
         <v>3384</v>
       </c>
-      <c r="E12" t="n">
-        <v>522</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>508</v>
+        <v>340</v>
+      </c>
+      <c r="G12" t="n">
+        <v>16</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>113</v>
+      </c>
+      <c r="J12" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="13">
@@ -717,12 +873,20 @@
       <c r="D13" t="n">
         <v>1016</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>112</v>
       </c>
-      <c r="F13" t="n">
-        <v>16</v>
-      </c>
+      <c r="G13" t="n">
+        <v>16</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,11 +903,27 @@
       <c r="D14" t="n">
         <v>2308</v>
       </c>
-      <c r="E14" t="n">
-        <v>364</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F14" t="n">
-        <v>166</v>
+        <v>348</v>
+      </c>
+      <c r="G14" t="n">
+        <v>16</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>134</v>
+      </c>
+      <c r="J14" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="15">
@@ -761,11 +941,27 @@
       <c r="D15" t="n">
         <v>3144</v>
       </c>
-      <c r="E15" t="n">
-        <v>455</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F15" t="n">
         <v>362</v>
+      </c>
+      <c r="G15" t="n">
+        <v>16</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>16</v>
+      </c>
+      <c r="J15" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="16">
@@ -783,11 +979,27 @@
       <c r="D16" t="n">
         <v>3196</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
         <v>319</v>
       </c>
-      <c r="F16" t="n">
-        <v>16</v>
+      <c r="G16" t="n">
+        <v>16</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>424</v>
+      </c>
+      <c r="J16" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="17">
@@ -805,12 +1017,20 @@
       <c r="D17" t="n">
         <v>664</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
         <v>79</v>
       </c>
-      <c r="F17" t="n">
-        <v>16</v>
-      </c>
+      <c r="G17" t="n">
+        <v>16</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -827,12 +1047,12 @@
       <c r="D18" t="n">
         <v>1424</v>
       </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -849,12 +1069,20 @@
       <c r="D19" t="n">
         <v>2320</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
         <v>92</v>
       </c>
-      <c r="F19" t="n">
-        <v>16</v>
-      </c>
+      <c r="G19" t="n">
+        <v>16</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -871,10 +1099,26 @@
       <c r="D20" t="n">
         <v>4652</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>488</v>
+      </c>
+      <c r="G20" t="n">
+        <v>14</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
         <v>589</v>
       </c>
-      <c r="F20" t="n">
+      <c r="J20" t="n">
         <v>16</v>
       </c>
     </row>
@@ -893,11 +1137,27 @@
       <c r="D21" t="n">
         <v>2972</v>
       </c>
-      <c r="E21" t="n">
-        <v>510</v>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F21" t="n">
-        <v>265</v>
+        <v>249</v>
+      </c>
+      <c r="G21" t="n">
+        <v>16</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>494</v>
+      </c>
+      <c r="J21" t="n">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
